--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99380</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -896,7 +896,7 @@
         <v>136088399</v>
       </c>
       <c r="B4" t="n">
-        <v>99380</v>
+        <v>99381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136088261</v>
       </c>
       <c r="B5" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136088454</v>
       </c>
       <c r="B6" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136088807</v>
       </c>
       <c r="B7" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>136089082</v>
       </c>
       <c r="B8" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         <v>136089236</v>
       </c>
       <c r="B9" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         <v>136089393</v>
       </c>
       <c r="B10" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1656,6 +1656,118 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136089393</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136920108</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Halvar-Jonsberget, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>479421</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6861087</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvros</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136920108</t>
         </is>
       </c>
     </row>
@@ -1670,6 +1782,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33969-2026 artfynd.xlsx
+++ b/artfynd/A 33969-2026 artfynd.xlsx
@@ -1664,7 +1664,7 @@
         <v>136920108</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
